--- a/mistral_translate_work/split_by_prompt/excel/ui/lang_guide_new/lang_guide_new__ui__part_0001.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/ui/lang_guide_new/lang_guide_new__ui__part_0001.xlsx
@@ -1363,7 +1363,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Hướng dẫn Chuyển Weapon.
+          <t>Hướng dẫn chuyển Vũ khí.
 Chạm {0} để mở trang Resonator.</t>
         </is>
       </c>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Sinh vật đột biến mạnh mẽ sống ở Cao nguyên Desorock. Thường xuất hiện trên đỉnh những ngọn núi cao chót vót và có ý thức lãnh thổ mạnh mẽ.</t>
+          <t>Sinh vật đột biến mạnh mẽ sống ở Desorock Highland. Thường xuất hiện trên đỉnh những ngọn núi cao chót vót và có ý thức lãnh thổ mạnh mẽ.</t>
         </is>
       </c>
     </row>
@@ -4841,7 +4841,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Chạm để mở Điều Chỉnh.</t>
+          <t>Chạm để mở Modulation.</t>
         </is>
       </c>
     </row>
@@ -4906,7 +4906,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Chạm để mở Điều Chỉnh.</t>
+          <t>Chạm để mở Modulation.</t>
         </is>
       </c>
     </row>
@@ -4971,7 +4971,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Chạm để mở trang Weapon.</t>
+          <t>Chạm để mở trang Vũ khí.</t>
         </is>
       </c>
     </row>
@@ -5231,7 +5231,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Chạm để mở trang Weapon.</t>
+          <t>Chạm để mở trang Vũ khí.</t>
         </is>
       </c>
     </row>
